--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512477_ELIMINGRE14FINAL_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2512477_ELIMINGRE14FINAL_PROCESSED.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0363</v>
+        <v>4.8831</v>
       </c>
       <c r="E2" t="n">
-        <v>1.0854</v>
+        <v>2.2684</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9509</v>
+        <v>2.6147</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1255</v>
+        <v>2.0509</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3258</v>
+        <v>0.2272</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7997</v>
+        <v>1.8237</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3851</v>
+        <v>2.5086</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1415</v>
+        <v>1.2034</v>
       </c>
       <c r="L2" t="n">
-        <v>1.2436</v>
+        <v>1.3052</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2596</v>
+        <v>-0.4577</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8157</v>
+        <v>-0.9762</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5561</v>
+        <v>0.5185</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4004</v>
+        <v>-1.3632</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R2" t="n">
-        <v>1.6005</v>
+        <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9716</v>
+        <v>0.8117</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.218</v>
+        <v>-0.3202</v>
       </c>
       <c r="U2" t="n">
-        <v>2.1896</v>
+        <v>1.1319</v>
       </c>
       <c r="V2" t="n">
-        <v>3.3395</v>
+        <v>3.3837</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9191</v>
+        <v>3.0011</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4204</v>
+        <v>0.3826</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9756</v>
+        <v>3.6612</v>
       </c>
       <c r="E3" t="n">
-        <v>3.8757</v>
+        <v>4.5855</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9001</v>
+        <v>-0.9243</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7845</v>
+        <v>2.7937</v>
       </c>
       <c r="H3" t="n">
-        <v>0.891</v>
+        <v>0.9021</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8934</v>
+        <v>1.8916</v>
       </c>
       <c r="J3" t="n">
-        <v>3.143</v>
+        <v>3.2647</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2633</v>
+        <v>1.3599</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8797</v>
+        <v>1.9047</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3585</v>
+        <v>-0.4709</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3722</v>
+        <v>-0.4578</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4004</v>
+        <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9494</v>
+        <v>-0.2162</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3867</v>
+        <v>0.1514</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5627</v>
+        <v>-0.3676</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2598</v>
+        <v>-0.2795</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1195</v>
+        <v>1.1695</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3793</v>
+        <v>-1.449</v>
       </c>
     </row>
     <row r="4">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3995</v>
+        <v>2.4474</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3995</v>
+        <v>2.4474</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3995</v>
+        <v>2.4474</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1997</v>
+        <v>1.2316</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3995</v>
+        <v>2.4474</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1997</v>
+        <v>1.2316</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1998</v>
+        <v>1.2158</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. GARCIA ROYO</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0694</v>
+        <v>2.3325</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8223</v>
+        <v>2.517</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2472</v>
+        <v>-0.1845</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9224</v>
+        <v>1.9793</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8064</v>
+        <v>2.2224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.116</v>
+        <v>-0.2432</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5249</v>
+        <v>2.7173</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8431</v>
+        <v>2.6684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6818</v>
+        <v>0.0489</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3975</v>
+        <v>-0.738</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0367</v>
+        <v>-0.446</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4342</v>
+        <v>-0.292</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6002</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0003</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4001</v>
+        <v>0.1947</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2528</v>
+        <v>0.1585</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7023</v>
+        <v>-0.2003</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4495</v>
+        <v>0.3588</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>D. GARCIA ROYO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5545</v>
+        <v>2.2354</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0296</v>
+        <v>1.2095</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4751</v>
+        <v>1.026</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9802</v>
+        <v>2.9214</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2201</v>
+        <v>1.8356</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.24</v>
+        <v>1.0859</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6031</v>
+        <v>2.6686</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5993</v>
+        <v>1.9552</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0038</v>
+        <v>0.7134</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6229</v>
+        <v>0.2528</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3791</v>
+        <v>-0.1197</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2438</v>
+        <v>0.3725</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2001</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.2001</v>
+        <v>0.3895</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6257</v>
+        <v>-0.1018</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5734</v>
+        <v>-0.4854</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0523</v>
+        <v>0.3837</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4357</v>
+        <v>1.3929</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4081</v>
+        <v>0.5923</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0276</v>
+        <v>0.8006</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2999</v>
+        <v>0.3063</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2647</v>
+        <v>1.2479</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9648</v>
+        <v>-0.9416</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09080000000000001</v>
+        <v>0.047</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3014</v>
+        <v>1.3676</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3922</v>
+        <v>-1.3207</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3907</v>
+        <v>0.2594</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0367</v>
+        <v>-0.1197</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4274</v>
+        <v>0.379</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5233</v>
+        <v>-0.6613</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1599</v>
+        <v>-0.2289</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3634</v>
+        <v>-0.4324</v>
       </c>
       <c r="V7" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="W7" t="n">
-        <v>2.6593</v>
+        <v>2.7216</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CAMPOS DE BENGOA</t>
+          <t>J. VILLAR SOLER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8341</v>
+        <v>0.9238</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2839</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>2.118</v>
+        <v>-0.0395</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1233</v>
+        <v>0.8232</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5614</v>
+        <v>0.2832</v>
       </c>
       <c r="I8" t="n">
-        <v>0.438</v>
+        <v>0.54</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7144</v>
+        <v>1.0112</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1963</v>
+        <v>0.4516</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.518</v>
+        <v>0.5596</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.409</v>
+        <v>-0.1881</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.365</v>
+        <v>-0.1684</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9560999999999999</v>
+        <v>-0.0197</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0003</v>
+        <v>0.7789</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0003</v>
+        <v>0.7789</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4376</v>
+        <v>-0.6784</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0891</v>
+        <v>-0.048</v>
       </c>
       <c r="U8" t="n">
-        <v>1.5267</v>
+        <v>-0.6304</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VILLAR SOLER</t>
+          <t>J. CAMPOS DE BENGOA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3146</v>
+        <v>0.8915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4743</v>
+        <v>-0.6015</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1597</v>
+        <v>1.493</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8312</v>
+        <v>-1.2131</v>
       </c>
       <c r="H9" t="n">
-        <v>0.325</v>
+        <v>-1.6344</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5062</v>
+        <v>0.4213</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9255</v>
+        <v>-0.6409</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4399</v>
+        <v>-0.1385</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4856</v>
+        <v>-0.5024</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.5722</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1149</v>
+        <v>-1.496</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0206</v>
+        <v>0.9237</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8002</v>
+        <v>0.9737</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8002</v>
+        <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3168</v>
+        <v>0.572</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4512</v>
+        <v>-0.5196</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8656</v>
+        <v>1.0916</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1549</v>
+        <v>0.1793</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1549</v>
+        <v>0.1793</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1216,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2712</v>
+        <v>0.2658</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1163</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1163</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4353</v>
+        <v>0.014</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7654</v>
+        <v>-0.4143</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3301</v>
+        <v>0.4283</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1712</v>
+        <v>-0.1637</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3312</v>
+        <v>0.3274</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5024</v>
+        <v>-0.4911</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0564</v>
+        <v>0.0047</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5816</v>
+        <v>0.6287</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1149</v>
+        <v>-0.1684</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2505</v>
+        <v>-0.3013</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1356</v>
+        <v>0.1329</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8642</v>
+        <v>-0.4065</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.709</v>
+        <v>-0.419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1552</v>
+        <v>0.0125</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1033</v>
+        <v>-1.311</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1949</v>
+        <v>-2.2208</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0915</v>
+        <v>0.9099</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.12</v>
+        <v>-0.1242</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0713</v>
+        <v>0.0605</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1912</v>
+        <v>-0.1847</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3545</v>
+        <v>-0.2704</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2435</v>
+        <v>0.3131</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.598</v>
+        <v>-0.5835</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2345</v>
+        <v>0.1461</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1723</v>
+        <v>-0.2526</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4068</v>
+        <v>0.3987</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2001</v>
+        <v>0.1947</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5032</v>
+        <v>-0.7194</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1599</v>
+        <v>-0.3147</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3433</v>
+        <v>-0.4047</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2414</v>
+        <v>-1.9867</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6368</v>
+        <v>-1.4084</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6047</v>
+        <v>-0.5783</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5037</v>
+        <v>-0.5605</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.3799</v>
+        <v>-0.39</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1238</v>
+        <v>-0.1705</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8616</v>
+        <v>0.9144</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7416</v>
+        <v>0.7929</v>
       </c>
       <c r="L13" t="n">
-        <v>0.12</v>
+        <v>0.1216</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.3653</v>
+        <v>-1.4749</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1215</v>
+        <v>-1.1829</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2438</v>
+        <v>-0.292</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2006</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8002</v>
+        <v>0.7789</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5432</v>
+        <v>0.7674</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5828</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0396</v>
+        <v>0.1177</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0803</v>
+        <v>-0.0516</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.6011</v>
+        <v>-2.4117</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0732</v>
+        <v>0.267</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.6743</v>
+        <v>-2.6786</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1518</v>
+        <v>1.1056</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3207</v>
+        <v>0.2724</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7033</v>
+        <v>1.7936</v>
       </c>
       <c r="K14" t="n">
-        <v>1.0215</v>
+        <v>1.0802</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6818</v>
+        <v>0.7134</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5515</v>
+        <v>-0.6879999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7009</v>
+        <v>-0.8078</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1493</v>
+        <v>0.1198</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.0006</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0009</v>
+        <v>-2.921</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3875</v>
+        <v>0.5927</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0888</v>
+        <v>-0.1061</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4763</v>
+        <v>0.6989</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.1398</v>
+        <v>-2.1626</v>
       </c>
       <c r="W14" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.5993</v>
+        <v>-3.6632</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.3935</v>
+        <v>13.2517</v>
       </c>
       <c r="E15" t="n">
-        <v>6.2871</v>
+        <v>10.2053</v>
       </c>
       <c r="F15" t="n">
-        <v>5.106299999999999</v>
+        <v>3.046599999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>12.848</v>
+        <v>12.6321</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8146</v>
+        <v>6.585900000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>6.033200000000001</v>
+        <v>6.046199999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>15.3299</v>
+        <v>16.4662</v>
       </c>
       <c r="K15" t="n">
-        <v>12.1801</v>
+        <v>12.9141</v>
       </c>
       <c r="L15" t="n">
-        <v>3.149900000000001</v>
+        <v>3.552</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4821</v>
+        <v>-3.834099999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.3655</v>
+        <v>-6.328400000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8834</v>
+        <v>2.4941</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0008</v>
+        <v>-2.9212</v>
       </c>
       <c r="Q15" t="n">
-        <v>-13.0039</v>
+        <v>-12.6578</v>
       </c>
       <c r="R15" t="n">
-        <v>10.0029</v>
+        <v>9.736799999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8118</v>
+        <v>0.0321999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.955500000000001</v>
+        <v>-1.8411</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1437</v>
+        <v>1.873499999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3583</v>
+        <v>3.508500000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>7.916599999999999</v>
+        <v>8.238000000000001</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.5582</v>
+        <v>-4.7296</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3109</v>
+        <v>1.7065</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6105</v>
+        <v>2.0822</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2996</v>
+        <v>-0.3757</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0692</v>
+        <v>1.0466</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2643</v>
+        <v>-0.2776</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3335</v>
+        <v>1.3243</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3195</v>
+        <v>2.3637</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9997</v>
+        <v>1.0263</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3198</v>
+        <v>1.3374</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2503</v>
+        <v>-1.3171</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.264</v>
+        <v>-1.3039</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0137</v>
+        <v>-0.0131</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6002</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2385</v>
+        <v>0.1977</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.709</v>
+        <v>-0.2815</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4705</v>
+        <v>0.4792</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. CLOSSET MARTINEZ</t>
+          <t>S. GOMEZ VELEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8012</v>
+        <v>0.3599</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3098</v>
+        <v>1.764</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-1.4041</v>
       </c>
       <c r="G17" t="n">
-        <v>-3.0007</v>
+        <v>0.5889</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.5072</v>
+        <v>-1.1669</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.4935</v>
+        <v>1.7558</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3506</v>
+        <v>2.5401</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1145</v>
+        <v>0.7647</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.236</v>
+        <v>1.7754</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6502</v>
+        <v>-1.9512</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3927</v>
+        <v>-1.9316</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2575</v>
+        <v>-0.0197</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8002</v>
+        <v>1.9474</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8002</v>
+        <v>1.9474</v>
       </c>
       <c r="S17" t="n">
-        <v>1.802</v>
+        <v>-0.2226</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4606</v>
+        <v>-0.7762</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3414</v>
+        <v>0.5535</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1998</v>
+        <v>-1.9537</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.9537</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3103</v>
+        <v>0.192</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2133</v>
+        <v>3.5282</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.903</v>
+        <v>-3.3363</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7938</v>
+        <v>0.9312</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7957</v>
+        <v>0.9557</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0019</v>
+        <v>-0.0244</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8738</v>
+        <v>3.185</v>
       </c>
       <c r="K18" t="n">
-        <v>2.232</v>
+        <v>2.5122</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6418</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.08</v>
+        <v>-2.2538</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4363</v>
+        <v>-1.5565</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6437</v>
+        <v>-0.6973</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2003</v>
+        <v>1.1684</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2006</v>
+        <v>2.1421</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7553</v>
+        <v>0.605</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1198</v>
+        <v>-0.1836</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8752</v>
+        <v>0.7886</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.4392</v>
+        <v>-2.5126</v>
       </c>
       <c r="W18" t="n">
-        <v>1.4596</v>
+        <v>1.5005</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.8988</v>
+        <v>-4.0132</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. GOMEZ VELEZ</t>
+          <t>R. MARTINEZ BERTOMEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1167</v>
+        <v>0.0508</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1442</v>
+        <v>0.2666</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0275</v>
+        <v>-0.2158</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5325</v>
+        <v>0.1837</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1735</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.706</v>
+        <v>0.2658</v>
       </c>
       <c r="J19" t="n">
-        <v>2.3689</v>
+        <v>0.3284</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6834</v>
+        <v>0.3284</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6855</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8363</v>
+        <v>-0.1447</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.8569</v>
+        <v>-0.4105</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0206</v>
+        <v>0.2658</v>
       </c>
       <c r="P19" t="n">
-        <v>2.0006</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0006</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4968</v>
+        <v>-0.1329</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2247</v>
+        <v>-0.0618</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7279</v>
+        <v>-0.0711</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9196</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.9196</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. MARTINEZ BERTOMEU</t>
+          <t>D. CLOSSET MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0556</v>
+        <v>-0.3392</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2555</v>
+        <v>0.3404</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1998</v>
+        <v>-0.6796</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1912</v>
+        <v>-2.958</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.08</v>
+        <v>-1.4717</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2712</v>
+        <v>-1.4864</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3199</v>
+        <v>-1.2304</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3199</v>
+        <v>-0.023</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-1.2074</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1287</v>
+        <v>-1.7276</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3999</v>
+        <v>-1.4487</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2712</v>
+        <v>-0.2789</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1356</v>
+        <v>0.6188</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0645</v>
+        <v>0.3498</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0711</v>
+        <v>0.269</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. DESPLACE</t>
+          <t>S. JIMENA LLORCA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6692</v>
+        <v>-0.4969</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3397</v>
+        <v>0.978</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6705</v>
+        <v>-1.4749</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.2155</v>
+        <v>-0.9451000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3912</v>
+        <v>1.6498</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6066</v>
+        <v>-2.5949</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3145</v>
+        <v>1.0851</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0415</v>
+        <v>2.9892</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.356</v>
+        <v>-1.9041</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.901</v>
+        <v>-2.0302</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6503</v>
+        <v>-1.3394</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2506</v>
+        <v>-0.6907</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0006</v>
+        <v>1.5579</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.0009</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0003</v>
+        <v>1.5579</v>
       </c>
       <c r="S21" t="n">
-        <v>1.007</v>
+        <v>0.3909</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7759</v>
+        <v>-0.107</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2311</v>
+        <v>0.4979</v>
       </c>
       <c r="V21" t="n">
-        <v>1.5399</v>
+        <v>-1.5005</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1998</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3401</v>
+        <v>-1.5005</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>T. DESPLACE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.568</v>
+        <v>-1.0366</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8786</v>
+        <v>-1.5544</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6894</v>
+        <v>0.5179</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4842</v>
+        <v>-1.2255</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7777</v>
+        <v>0.389</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2935</v>
+        <v>-1.6145</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7018</v>
+        <v>-0.2283</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.578</v>
+        <v>1.1008</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2798</v>
+        <v>-1.329</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1859</v>
+        <v>-0.9973</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1997</v>
+        <v>-0.7118</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0137</v>
+        <v>-0.2855</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6002</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.0003</v>
+        <v>-2.921</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4001</v>
+        <v>0.9737</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4837</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.3738</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0964</v>
+        <v>0.2104</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.5521</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. AGBEKO</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7853</v>
+        <v>-1.2061</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9909</v>
+        <v>-0.4962</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2057</v>
+        <v>-0.7099</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.2642</v>
+        <v>-0.5097</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4155</v>
+        <v>-1.7935</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8486</v>
+        <v>1.2837</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.8343</v>
+        <v>0.735</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2363</v>
+        <v>-0.5619</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.598</v>
+        <v>1.2968</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4298</v>
+        <v>-1.2447</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1792</v>
+        <v>-1.2316</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2506</v>
+        <v>-0.0131</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6005</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0009</v>
+        <v>-0.9737</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4004</v>
+        <v>0.3895</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8196</v>
+        <v>-0.1121</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3247</v>
+        <v>-0.2575</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4949</v>
+        <v>0.1454</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2598</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5196</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. JIMENA LLORCA</t>
+          <t>R. AGBEKO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.7975</v>
+        <v>-2.1867</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2627</v>
+        <v>-3.0845</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5348</v>
+        <v>0.8978</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.003</v>
+        <v>-1.2892</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6377</v>
+        <v>-0.4203</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.6408</v>
+        <v>-0.8689</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8908</v>
+        <v>-0.763</v>
       </c>
       <c r="K24" t="n">
-        <v>2.881</v>
+        <v>-0.1795</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9902</v>
+        <v>-0.5835</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8938</v>
+        <v>-0.5262</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2433</v>
+        <v>-0.2407</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6506</v>
+        <v>-0.2855</v>
       </c>
       <c r="P24" t="n">
-        <v>1.6005</v>
+        <v>-1.5579</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R24" t="n">
-        <v>1.6005</v>
+        <v>1.3632</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9353</v>
+        <v>0.3809</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1535</v>
+        <v>0.0406</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2182</v>
+        <v>0.3403</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4596</v>
+        <v>0.2795</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4596</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.6909</v>
+        <v>-2.3451</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.0644</v>
+        <v>-2.9802</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3735</v>
+        <v>0.6351</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.7344</v>
+        <v>-3.6654</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7766</v>
+        <v>-1.7041</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.9578</v>
+        <v>-1.9614</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.0612</v>
+        <v>-1.8103</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.06909999999999999</v>
+        <v>0.1182</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.9921</v>
+        <v>-1.9286</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.6732</v>
+        <v>-1.8551</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.7075</v>
+        <v>-1.8223</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0343</v>
+        <v>-0.0328</v>
       </c>
       <c r="P25" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0006</v>
+        <v>1.9474</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6964</v>
+        <v>-0.4213</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.8626</v>
+        <v>-1.0863</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1661</v>
+        <v>0.6649</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7397</v>
+        <v>0.7679</v>
       </c>
       <c r="W25" t="n">
-        <v>0.8597</v>
+        <v>0.89</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.12</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.4775</v>
+        <v>-5.4308</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1032</v>
+        <v>-3.8907</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3743</v>
+        <v>-1.5401</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.7328</v>
+        <v>-4.7895</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6444</v>
+        <v>-2.6643</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.0885</v>
+        <v>-2.1253</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.4321</v>
+        <v>-2.3712</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.7941</v>
+        <v>-1.7472</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.638</v>
+        <v>-0.624</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.3007</v>
+        <v>-2.4183</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.9171</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.4505</v>
+        <v>-1.5013</v>
       </c>
       <c r="P26" t="n">
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0003</v>
+        <v>-0.9737</v>
       </c>
       <c r="R26" t="n">
-        <v>1.0003</v>
+        <v>0.9737</v>
       </c>
       <c r="S26" t="n">
-        <v>1.4145</v>
+        <v>0.5988</v>
       </c>
       <c r="T26" t="n">
-        <v>1.0094</v>
+        <v>0.1163</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4051</v>
+        <v>0.4824</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.1591</v>
+        <v>-1.24</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.6802</v>
+        <v>-0.6621</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.4789</v>
+        <v>-0.5779</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-11.3937</v>
+        <v>-10.7322</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.106199999999999</v>
+        <v>-3.0466</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.2873</v>
+        <v>-7.6856</v>
       </c>
       <c r="G27" t="n">
-        <v>-12.8481</v>
+        <v>-12.632</v>
       </c>
       <c r="H27" t="n">
-        <v>-6.8146</v>
+        <v>-6.586</v>
       </c>
       <c r="I27" t="n">
-        <v>-6.0335</v>
+        <v>-6.0462</v>
       </c>
       <c r="J27" t="n">
-        <v>2.482000000000001</v>
+        <v>3.834100000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>5.3655</v>
+        <v>6.328200000000002</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.8834</v>
+        <v>-2.4941</v>
       </c>
       <c r="M27" t="n">
-        <v>-15.3299</v>
+        <v>-16.4662</v>
       </c>
       <c r="N27" t="n">
-        <v>-12.1801</v>
+        <v>-12.9141</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.15</v>
+        <v>-3.5521</v>
       </c>
       <c r="P27" t="n">
-        <v>3.000800000000001</v>
+        <v>2.921</v>
       </c>
       <c r="Q27" t="n">
-        <v>-10.003</v>
+        <v>-9.736799999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>13.0038</v>
+        <v>12.658</v>
       </c>
       <c r="S27" t="n">
-        <v>1.8121</v>
+        <v>2.4874</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.143599999999999</v>
+        <v>-1.8734</v>
       </c>
       <c r="U27" t="n">
-        <v>3.9557</v>
+        <v>4.3605</v>
       </c>
       <c r="V27" t="n">
-        <v>-3.3583</v>
+        <v>-3.508299999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>4.5583</v>
+        <v>4.7296</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.916600000000001</v>
+        <v>-8.2379</v>
       </c>
     </row>
   </sheetData>
